--- a/Sindhi Muslim/Miss Fatima/Report.xlsx
+++ b/Sindhi Muslim/Miss Fatima/Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Miss Fatima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4A8DDE-4EAB-40E1-B8FB-32E60A4DE53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA5066E-6A78-4812-B856-701CBC2F3C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{E5D688D1-49AB-4339-BB9B-121021F64726}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5D688D1-49AB-4339-BB9B-121021F64726}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>S No</t>
   </si>
@@ -138,9 +138,6 @@
     <t>Hafsa Jamali</t>
   </si>
   <si>
-    <t>Hafsa</t>
-  </si>
-  <si>
     <t>Insha</t>
   </si>
   <si>
@@ -157,9 +154,6 @@
   </si>
   <si>
     <t>Sehrish Ali</t>
-  </si>
-  <si>
-    <t>Shafia</t>
   </si>
   <si>
     <t>Sughra</t>
@@ -226,7 +220,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -311,17 +305,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -349,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -384,13 +367,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -400,32 +380,13 @@
   <dxfs count="10">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
+        <color rgb="FF9C0006"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -607,6 +568,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -614,15 +584,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -630,13 +591,32 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -652,8 +632,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B376D344-63B1-4E02-96B9-1BBCE29A10C0}" name="Table1" displayName="Table1" ref="A1:E47" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:E47" xr:uid="{B376D344-63B1-4E02-96B9-1BBCE29A10C0}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B376D344-63B1-4E02-96B9-1BBCE29A10C0}" name="Table1" displayName="Table1" ref="A1:E43" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:E43" xr:uid="{B376D344-63B1-4E02-96B9-1BBCE29A10C0}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -968,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58932A9E-E83D-4DD4-9FA7-2D643BE62397}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="5" customWidth="1"/>
@@ -1006,7 +986,9 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>10</v>
+      </c>
       <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1019,7 +1001,9 @@
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>9</v>
+      </c>
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1032,7 +1016,9 @@
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>9</v>
+      </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1045,7 +1031,9 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1058,7 +1046,9 @@
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2">
+        <v>9</v>
+      </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1071,7 +1061,9 @@
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2">
+        <v>9</v>
+      </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1084,7 +1076,9 @@
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2">
+        <v>10</v>
+      </c>
       <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1097,7 +1091,9 @@
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2">
+        <v>9</v>
+      </c>
       <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1110,7 +1106,9 @@
       <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2">
+        <v>9</v>
+      </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1118,25 +1116,29 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10</v>
+      </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
-        <v>653</v>
+      <c r="B12" s="2">
+        <v>657</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9</v>
+      </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1144,12 +1146,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="D13" s="2">
+        <v>9</v>
+      </c>
       <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1157,12 +1161,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>672</v>
+        <v>702</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="D14" s="2">
+        <v>9</v>
+      </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1170,12 +1176,14 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>702</v>
+        <v>659</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="D15" s="2">
+        <v>9</v>
+      </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1183,12 +1191,14 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="D16" s="2">
+        <v>9</v>
+      </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1196,12 +1206,14 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>661</v>
+        <v>522</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="D17" s="2">
+        <v>10</v>
+      </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1209,12 +1221,14 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>522</v>
+        <v>654</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="D18" s="2">
+        <v>9</v>
+      </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1222,12 +1236,14 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="D19" s="2">
+        <v>10</v>
+      </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1235,12 +1251,14 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>660</v>
+        <v>841</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="D20" s="2">
+        <v>10</v>
+      </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1248,12 +1266,14 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>841</v>
+        <v>676</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="D21" s="2">
+        <v>9</v>
+      </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1261,12 +1281,14 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="D22" s="2">
+        <v>9</v>
+      </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1274,12 +1296,14 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>658</v>
+        <v>785</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D23" s="2">
+        <v>9</v>
+      </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1287,12 +1311,14 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>785</v>
+        <v>544</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="D24" s="2">
+        <v>10</v>
+      </c>
       <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1300,12 +1326,14 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>544</v>
+        <v>780</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="D25" s="2">
+        <v>10</v>
+      </c>
       <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1313,12 +1341,14 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>780</v>
+        <v>844</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="D26" s="2">
+        <v>11</v>
+      </c>
       <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1326,12 +1356,14 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>844</v>
+        <v>569</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="D27" s="2">
+        <v>10</v>
+      </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1339,12 +1371,14 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="D28" s="2">
+        <v>10</v>
+      </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1352,12 +1386,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="2">
         <v>11</v>
       </c>
-      <c r="D29" s="2"/>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1365,12 +1401,14 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>574</v>
+        <v>526</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="D30" s="2">
+        <v>9</v>
+      </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1378,12 +1416,14 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="D31" s="2">
+        <v>10</v>
+      </c>
       <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1391,12 +1431,14 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>914</v>
+        <v>520</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="D32" s="2">
+        <v>11</v>
+      </c>
       <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1404,12 +1446,14 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>537</v>
+        <v>915</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" s="2">
+        <v>10</v>
+      </c>
       <c r="E33" s="7"/>
     </row>
     <row r="34" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1417,12 +1461,14 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>584</v>
+        <v>687</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="D34" s="2">
+        <v>10</v>
+      </c>
       <c r="E34" s="7"/>
     </row>
     <row r="35" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1430,12 +1476,14 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>520</v>
+        <v>649</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="D35" s="2">
+        <v>12</v>
+      </c>
       <c r="E35" s="7"/>
     </row>
     <row r="36" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1443,12 +1491,14 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>915</v>
+        <v>686</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D36" s="2">
+        <v>11</v>
+      </c>
       <c r="E36" s="7"/>
     </row>
     <row r="37" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1456,12 +1506,14 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>687</v>
+        <v>581</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="D37" s="2">
+        <v>10</v>
+      </c>
       <c r="E37" s="7"/>
     </row>
     <row r="38" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1469,12 +1521,14 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>649</v>
+        <v>525</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="D38" s="2">
+        <v>10</v>
+      </c>
       <c r="E38" s="7"/>
     </row>
     <row r="39" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1482,12 +1536,14 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>686</v>
+        <v>577</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="D39" s="2">
+        <v>11</v>
+      </c>
       <c r="E39" s="7"/>
     </row>
     <row r="40" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1495,12 +1551,14 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="D40" s="2">
+        <v>12</v>
+      </c>
       <c r="E40" s="7"/>
     </row>
     <row r="41" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1508,12 +1566,14 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>588</v>
+        <v>912</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="D41" s="2">
+        <v>12</v>
+      </c>
       <c r="E41" s="7"/>
     </row>
     <row r="42" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1521,82 +1581,34 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>525</v>
+        <v>571</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="D42" s="2">
+        <v>11</v>
+      </c>
       <c r="E42" s="7"/>
     </row>
     <row r="43" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="2">
-        <v>577</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2">
-        <v>589</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="B43" s="11">
+        <v>572</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2">
-        <v>912</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2">
-        <v>571</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="1:5" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46</v>
-      </c>
-      <c r="B47" s="12">
-        <v>572</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="14"/>
+      <c r="D43" s="11">
+        <v>12</v>
+      </c>
+      <c r="E43" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B25:B47">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  <conditionalFormatting sqref="B24:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
